--- a/서버정보/20261002_리소스배포_운영.xlsx
+++ b/서버정보/20261002_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D225C1A-F052-4A4A-9992-4A7832767B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150CB281-0E04-45F0-8080-88ECA576E9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -6618,7 +6618,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6986,18 +6986,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -28967,7 +28955,6 @@
       <c r="AF159" s="74"/>
     </row>
     <row r="160" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A160" s="125"/>
       <c r="B160" s="95" t="s">
         <v>23</v>
       </c>
@@ -29055,8 +29042,7 @@
       <c r="AE160" s="74"/>
       <c r="AF160" s="74"/>
     </row>
-    <row r="161" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A161" s="125"/>
+    <row r="161" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B161" s="95" t="s">
         <v>23</v>
       </c>
@@ -29144,15 +29130,15 @@
       <c r="AE161" s="95"/>
       <c r="AF161" s="95"/>
     </row>
-    <row r="162" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B162" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C162" s="123" t="str" cm="1">
+      <c r="C162" s="95" t="str" cm="1">
         <f t="array" ref="C162">UPPER(INDEX(_xlfn.TEXTSPLIT($F162, "-"), 3))</f>
         <v>GA</v>
       </c>
-      <c r="D162" s="123" t="s">
+      <c r="D162" s="95" t="s">
         <v>1165</v>
       </c>
       <c r="E162" s="74" t="s">
@@ -29185,7 +29171,7 @@
       <c r="N162" s="121" t="s">
         <v>1178</v>
       </c>
-      <c r="O162" s="124" t="str">
+      <c r="O162" s="120" t="str">
         <f>SUBSTITUTE(F162,"hazr-","")&amp;"-osdisk"</f>
         <v>p-ga-oap01-osdisk</v>
       </c>
@@ -29195,10 +29181,10 @@
       <c r="Q162" s="113" t="s">
         <v>179</v>
       </c>
-      <c r="R162" s="123"/>
+      <c r="R162" s="95"/>
       <c r="S162" s="95"/>
-      <c r="T162" s="123"/>
-      <c r="U162" s="123" t="str">
+      <c r="T162" s="95"/>
+      <c r="U162" s="95" t="str">
         <f>SUBSTITUTE(F162,"hazr-","")&amp;"-nic"</f>
         <v>p-ga-oap01-nic</v>
       </c>
@@ -29232,15 +29218,15 @@
       <c r="AE162" s="95"/>
       <c r="AF162" s="95"/>
     </row>
-    <row r="163" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B163" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C163" s="123" t="str" cm="1">
+      <c r="C163" s="95" t="str" cm="1">
         <f t="array" ref="C163">UPPER(INDEX(_xlfn.TEXTSPLIT($F163, "-"), 3))</f>
         <v>GA</v>
       </c>
-      <c r="D163" s="123" t="s">
+      <c r="D163" s="95" t="s">
         <v>1165</v>
       </c>
       <c r="E163" s="95" t="s">
@@ -29273,7 +29259,7 @@
       <c r="N163" s="121" t="s">
         <v>1135</v>
       </c>
-      <c r="O163" s="124" t="str">
+      <c r="O163" s="120" t="str">
         <f>SUBSTITUTE(F163,"hazr-","")&amp;"-osdisk"</f>
         <v>p-ga-oap02-osdisk</v>
       </c>
@@ -29283,10 +29269,10 @@
       <c r="Q163" s="113" t="s">
         <v>179</v>
       </c>
-      <c r="R163" s="123"/>
+      <c r="R163" s="95"/>
       <c r="S163" s="95"/>
-      <c r="T163" s="123"/>
-      <c r="U163" s="123" t="str">
+      <c r="T163" s="95"/>
+      <c r="U163" s="95" t="str">
         <f>SUBSTITUTE(F163,"hazr-","")&amp;"-nic"</f>
         <v>p-ga-oap02-nic</v>
       </c>
@@ -29320,15 +29306,15 @@
       <c r="AE163" s="95"/>
       <c r="AF163" s="95"/>
     </row>
-    <row r="164" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B164" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C164" s="123" t="str" cm="1">
+      <c r="C164" s="95" t="str" cm="1">
         <f t="array" ref="C164">UPPER(INDEX(_xlfn.TEXTSPLIT($F164, "-"), 3))</f>
         <v>BSU</v>
       </c>
-      <c r="D164" s="123" t="s">
+      <c r="D164" s="95" t="s">
         <v>1166</v>
       </c>
       <c r="E164" s="74" t="s">
@@ -29361,7 +29347,7 @@
       <c r="N164" s="121" t="s">
         <v>1179</v>
       </c>
-      <c r="O164" s="124" t="str">
+      <c r="O164" s="120" t="str">
         <f>SUBSTITUTE(F164,"hazr-","")&amp;"-osdisk"</f>
         <v>p-bsu-accweb01-osdisk</v>
       </c>
@@ -29371,10 +29357,10 @@
       <c r="Q164" s="113" t="s">
         <v>179</v>
       </c>
-      <c r="R164" s="123"/>
+      <c r="R164" s="95"/>
       <c r="S164" s="95"/>
-      <c r="T164" s="123"/>
-      <c r="U164" s="123" t="str">
+      <c r="T164" s="95"/>
+      <c r="U164" s="95" t="str">
         <f>SUBSTITUTE(F164,"hazr-","")&amp;"-nic"</f>
         <v>p-bsu-accweb01-nic</v>
       </c>
@@ -38416,7 +38402,6 @@
       <c r="R168" s="80"/>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A169" s="126"/>
       <c r="B169" s="78" t="s">
         <v>23</v>
       </c>
@@ -38471,7 +38456,6 @@
       <c r="R169" s="78"/>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A170" s="126"/>
       <c r="B170" s="80" t="s">
         <v>23</v>
       </c>
@@ -43899,7 +43883,6 @@
       <c r="M130" s="73"/>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A131" s="125"/>
       <c r="B131" s="80" t="s">
         <v>23</v>
       </c>
@@ -43932,7 +43915,6 @@
       <c r="M131" s="74"/>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A132" s="125"/>
       <c r="B132" s="78" t="s">
         <v>23</v>
       </c>
@@ -44421,11 +44403,13 @@
       <c r="M146" s="73"/>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A147" s="125"/>
       <c r="B147" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="C147" s="80"/>
+      <c r="C147" s="80" t="str" cm="1">
+        <f t="array" ref="C147">UPPER(INDEX(_xlfn.TEXTSPLIT($E147, "-"), 2))</f>
+        <v>TM</v>
+      </c>
       <c r="D147" s="74" t="s">
         <v>317</v>
       </c>
@@ -44451,11 +44435,13 @@
       <c r="M147" s="74"/>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A148" s="125"/>
       <c r="B148" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="C148" s="78"/>
+      <c r="C148" s="78" t="str" cm="1">
+        <f t="array" ref="C148">UPPER(INDEX(_xlfn.TEXTSPLIT($E148, "-"), 2))</f>
+        <v>TM</v>
+      </c>
       <c r="D148" s="73" t="s">
         <v>317</v>
       </c>
@@ -44481,11 +44467,13 @@
       <c r="M148" s="73"/>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A149" s="125"/>
       <c r="B149" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="C149" s="80"/>
+      <c r="C149" s="80" t="str" cm="1">
+        <f t="array" ref="C149">UPPER(INDEX(_xlfn.TEXTSPLIT($E149, "-"), 2))</f>
+        <v>GA</v>
+      </c>
       <c r="D149" s="74" t="s">
         <v>317</v>
       </c>
@@ -44511,11 +44499,13 @@
       <c r="M149" s="74"/>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A150" s="125"/>
       <c r="B150" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="C150" s="78"/>
+      <c r="C150" s="78" t="str" cm="1">
+        <f t="array" ref="C150">UPPER(INDEX(_xlfn.TEXTSPLIT($E150, "-"), 2))</f>
+        <v>GA</v>
+      </c>
       <c r="D150" s="73" t="s">
         <v>317</v>
       </c>
@@ -54114,6 +54104,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -54257,35 +54262,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -54307,9 +54287,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20261002_리소스배포_운영.xlsx
+++ b/서버정보/20261002_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150CB281-0E04-45F0-8080-88ECA576E9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD2E3B63-DB7B-44F2-9F5E-26859EA9FFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -13935,6 +13935,7 @@
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A78" s="90"/>
       <c r="B78" s="74" t="s">
         <v>23</v>
       </c>
@@ -13996,6 +13997,7 @@
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A79" s="90"/>
       <c r="B79" s="82" t="s">
         <v>23</v>
       </c>
@@ -28955,6 +28957,7 @@
       <c r="AF159" s="74"/>
     </row>
     <row r="160" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A160" s="90"/>
       <c r="B160" s="95" t="s">
         <v>23</v>
       </c>
@@ -29042,7 +29045,8 @@
       <c r="AE160" s="74"/>
       <c r="AF160" s="74"/>
     </row>
-    <row r="161" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A161" s="90"/>
       <c r="B161" s="95" t="s">
         <v>23</v>
       </c>
@@ -29130,7 +29134,8 @@
       <c r="AE161" s="95"/>
       <c r="AF161" s="95"/>
     </row>
-    <row r="162" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A162" s="90"/>
       <c r="B162" s="95" t="s">
         <v>23</v>
       </c>
@@ -29218,7 +29223,8 @@
       <c r="AE162" s="95"/>
       <c r="AF162" s="95"/>
     </row>
-    <row r="163" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A163" s="90"/>
       <c r="B163" s="95" t="s">
         <v>23</v>
       </c>
@@ -29306,7 +29312,8 @@
       <c r="AE163" s="95"/>
       <c r="AF163" s="95"/>
     </row>
-    <row r="164" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A164" s="90"/>
       <c r="B164" s="95" t="s">
         <v>23</v>
       </c>
@@ -38402,6 +38409,7 @@
       <c r="R168" s="80"/>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A169" s="99"/>
       <c r="B169" s="78" t="s">
         <v>23</v>
       </c>
@@ -38456,6 +38464,7 @@
       <c r="R169" s="78"/>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A170" s="99"/>
       <c r="B170" s="80" t="s">
         <v>23</v>
       </c>
@@ -38510,6 +38519,7 @@
       <c r="R170" s="80"/>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A171" s="99"/>
       <c r="B171" s="78" t="s">
         <v>23</v>
       </c>
@@ -38564,6 +38574,7 @@
       <c r="R171" s="78"/>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A172" s="99"/>
       <c r="B172" s="80" t="s">
         <v>23</v>
       </c>
@@ -38618,6 +38629,7 @@
       <c r="R172" s="80"/>
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A173" s="99"/>
       <c r="B173" s="78" t="s">
         <v>23</v>
       </c>
@@ -43883,6 +43895,7 @@
       <c r="M130" s="73"/>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A131" s="90"/>
       <c r="B131" s="80" t="s">
         <v>23</v>
       </c>
@@ -43915,6 +43928,7 @@
       <c r="M131" s="74"/>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A132" s="90"/>
       <c r="B132" s="78" t="s">
         <v>23</v>
       </c>
@@ -44403,6 +44417,7 @@
       <c r="M146" s="73"/>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A147" s="90"/>
       <c r="B147" s="80" t="s">
         <v>23</v>
       </c>
@@ -44435,6 +44450,7 @@
       <c r="M147" s="74"/>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A148" s="90"/>
       <c r="B148" s="78" t="s">
         <v>23</v>
       </c>
@@ -44467,6 +44483,7 @@
       <c r="M148" s="73"/>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A149" s="90"/>
       <c r="B149" s="80" t="s">
         <v>23</v>
       </c>
@@ -44499,6 +44516,7 @@
       <c r="M149" s="74"/>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A150" s="90"/>
       <c r="B150" s="78" t="s">
         <v>23</v>
       </c>
@@ -45767,6 +45785,7 @@
       <c r="M181" s="74"/>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A182" s="90"/>
       <c r="B182" s="78" t="s">
         <v>23</v>
       </c>
@@ -45806,6 +45825,7 @@
       <c r="M182" s="73"/>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A183" s="90"/>
       <c r="B183" s="80" t="s">
         <v>23</v>
       </c>
@@ -45845,6 +45865,7 @@
       <c r="M183" s="74"/>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A184" s="90"/>
       <c r="B184" s="78" t="s">
         <v>23</v>
       </c>
@@ -45884,6 +45905,7 @@
       <c r="M184" s="73"/>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A185" s="90"/>
       <c r="B185" s="80" t="s">
         <v>23</v>
       </c>
@@ -45923,6 +45945,7 @@
       <c r="M185" s="74"/>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A186" s="90"/>
       <c r="B186" s="78" t="s">
         <v>23</v>
       </c>
@@ -51125,6 +51148,7 @@
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A51" s="90"/>
       <c r="B51" s="74" t="s">
         <v>23</v>
       </c>
@@ -51178,6 +51202,7 @@
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A52" s="90"/>
       <c r="B52" s="82" t="s">
         <v>23</v>
       </c>
@@ -53778,6 +53803,7 @@
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" s="90"/>
       <c r="B78" s="74" t="s">
         <v>23</v>
       </c>
@@ -53810,6 +53836,7 @@
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79" s="90"/>
       <c r="B79" s="82" t="s">
         <v>23</v>
       </c>
@@ -53842,6 +53869,7 @@
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80" s="90"/>
       <c r="B80" s="74" t="s">
         <v>23</v>
       </c>
@@ -53873,7 +53901,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A81" s="90"/>
       <c r="B81" s="82" t="s">
         <v>23</v>
       </c>
@@ -53905,7 +53934,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82" s="90"/>
       <c r="B82" s="82" t="s">
         <v>23</v>
       </c>
@@ -53937,7 +53967,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A83" s="90"/>
       <c r="B83" s="82" t="s">
         <v>23</v>
       </c>
@@ -53969,7 +54000,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84" s="90"/>
       <c r="B84" s="82" t="s">
         <v>23</v>
       </c>
@@ -54001,7 +54033,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A85" s="90"/>
       <c r="B85" s="82" t="s">
         <v>23</v>
       </c>
@@ -54033,7 +54066,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86" s="90"/>
       <c r="B86" s="82" t="s">
         <v>23</v>
       </c>
@@ -54065,7 +54099,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A87" s="90"/>
       <c r="B87" s="82" t="s">
         <v>23</v>
       </c>
@@ -54104,21 +54139,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -54262,10 +54282,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -54287,19 +54332,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>